--- a/inspection_forms/043_industrial_hygiene_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/043_industrial_hygiene_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'safety_manager',_'value':_'safety_manager'}</t>
+          <t>safety_manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Safety Manager', 'value': 'Safety Manager'}</t>
+          <t>Safety Manager</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'shift_manager',_'value':_'shift_manager'}</t>
+          <t>shift_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Shift Manager', 'value': 'Shift Manager'}</t>
+          <t>Shift Manager</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'plant_engineer',_'value':_'plant_engineer'}</t>
+          <t>plant_engineer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Plant Engineer', 'value': 'Plant Engineer'}</t>
+          <t>Plant Engineer</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'environmental_specialist',_'value':_'environmental_specialist'}</t>
+          <t>environmental_specialist</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Environmental Specialist', 'value': 'Environmental Specialist'}</t>
+          <t>Environmental Specialist</t>
         </is>
       </c>
     </row>
